--- a/assessment_forms/015_data_warehouse_assessment_questionnaire--assessment_forms.xlsx
+++ b/assessment_forms/015_data_warehouse_assessment_questionnaire--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1003,29 +1003,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>data_lineage</t>
+          <t>improvement_priorities</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Data Lineage</t>
+          <t>Improvement Priorities</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>governance_choices</t>
+          <t>improvement_priorities_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>improvement_priorities</t>
+          <t>data_quality</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Improvement Priorities</t>
+          <t>Data Quality</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>data_quality</t>
+          <t>data_lineage</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Data Quality</t>
+          <t>Data Lineage</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>data_lineage</t>
+          <t>refresh_frequency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Data Lineage</t>
+          <t>Refresh Frequency</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>refresh_frequency</t>
+          <t>governance_model</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Refresh Frequency</t>
+          <t>Governance Model</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>governance_model</t>
+          <t>stakeholder_feedback</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Governance Model</t>
+          <t>Stakeholder Feedback</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>stakeholder_feedback</t>
+          <t>improvement_priorities</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Stakeholder Feedback</t>
+          <t>Improvement Priorities</t>
         </is>
       </c>
     </row>
@@ -1122,29 +1122,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>improvement_priorities</t>
+          <t>data_warehouse_team</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Improvement Priorities</t>
+          <t>Data Warehouse Team</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>improvement_priorities_choices</t>
+          <t>governance_model_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>data_warehouse_team</t>
+          <t>centralized</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Data Warehouse Team</t>
+          <t>Centralized</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>centralized</t>
+          <t>decentralized</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Centralized</t>
+          <t>Decentralized</t>
         </is>
       </c>
     </row>
@@ -1173,29 +1173,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>decentralized</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Decentralized</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>governance_model_choices</t>
+          <t>refresh_frequency_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>once_a_week</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Once a week</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>once_a_week</t>
+          <t>once_a_month</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Once a week</t>
+          <t>Once a month</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>once_a_month</t>
+          <t>once_a_quarter</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Once a month</t>
+          <t>Once a quarter</t>
         </is>
       </c>
     </row>
@@ -1241,29 +1241,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>once_a_quarter</t>
+          <t>once_a_year</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Once a quarter</t>
+          <t>Once a year</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>refresh_frequency_choices</t>
+          <t>data_lineage_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>once_a_year</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Once a year</t>
+          <t>Data Source</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>data_warehouse</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Data Source</t>
+          <t>Data Warehouse</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>data_warehouse</t>
+          <t>data_model</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Data Warehouse</t>
+          <t>Data Model</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>data_model</t>
+          <t>data_quality</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Data Model</t>
+          <t>Data Quality</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>data_quality</t>
+          <t>data_lineage</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Data Quality</t>
+          <t>Data Lineage</t>
         </is>
       </c>
     </row>
@@ -1343,29 +1343,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>data_lineage</t>
+          <t>data_governance</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Data Lineage</t>
+          <t>Data Governance</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>data_lineage_choices</t>
+          <t>data_quality_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>data_governance</t>
+          <t>data_accuracy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Data Governance</t>
+          <t>Data Accuracy</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>data_accuracy</t>
+          <t>data_completeness</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Data Accuracy</t>
+          <t>Data Completeness</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>data_completeness</t>
+          <t>data_timeliness</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Data Completeness</t>
+          <t>Data Timeliness</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>data_timeliness</t>
+          <t>data_relevancy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Data Timeliness</t>
+          <t>Data Relevancy</t>
         </is>
       </c>
     </row>
@@ -1428,27 +1428,10 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>data_relevancy</t>
+          <t>data_integrity</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
-        <is>
-          <t>Data Relevancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>data_quality_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>data_integrity</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
         <is>
           <t>Data Integrity</t>
         </is>
